--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Antwortmöglichkeiten aus dem ATHIS Fragebogen (Österreichische Gesundheitsbefragung, STATISTIK AUSTRIA). Version vom 31.03.2025; Codes sind englisch; Display-Werte bleiben deutsch. Gruppiert nach Skalentypen für die Wiederverwendung in PreNUDGE Questionnaires. Hinweis: Bestehende PreNUDGE CodeSystems bleiben gültig – whoqol-bref-scale (LQ16-Zufriedenheitsskala), prenudge-nutrition-consumption-frequency (DH1/DH3 numerische ATHIS-Codes), prenudge-alcoholuse-frequency (AL1 SNOMED-basiert).</t>
+    <t>Vollständige Antwortmöglichkeiten aus dem ATHIS Fragebogen (Österreichische Gesundheitsbefragung, STATISTIK AUSTRIA, Version 31.03.2025). Codes sind englisch; Display-Werte bleiben deutsch. Gruppiert nach Skalentypen. Hinweis: Bestehende PreNUDGE CodeSystems bleiben gültig – whoqol-bref-scale (LQ16-Zufriedenheitsskala), prenudge-nutrition-consumption-frequency (DH1/DH3 numerische Codes), prenudge-alcoholuse-frequency (AL1 SNOMED-basiert).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -129,7 +129,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>111</t>
+    <t>262</t>
   </si>
   <si>
     <t>Level</t>
@@ -201,31 +201,73 @@
     <t>Nein, noch nie genutzt/konsumiert</t>
   </si>
   <si>
-    <t>hs-very-good</t>
+    <t>yn-severely-visually-impaired</t>
+  </si>
+  <si>
+    <t>Ich bin stark sehbehindert oder kann nicht sehen</t>
+  </si>
+  <si>
+    <t>yn-severely-hearing-impaired</t>
+  </si>
+  <si>
+    <t>Ich bin hochgradig schwerhörig oder gehörlos</t>
+  </si>
+  <si>
+    <t>yn-yes-at-least-one</t>
+  </si>
+  <si>
+    <t>Ja, bei mindestens einer Tätigkeit</t>
+  </si>
+  <si>
+    <t>yn-yes-at-least-once</t>
+  </si>
+  <si>
+    <t>Ja, mindestens einmal</t>
+  </si>
+  <si>
+    <t>yn-yes-always</t>
+  </si>
+  <si>
+    <t>Ja, jedes Mal</t>
+  </si>
+  <si>
+    <t>yn-no-not-always</t>
+  </si>
+  <si>
+    <t>Nein, mindestens einmal nicht</t>
+  </si>
+  <si>
+    <t>yn-no-need</t>
+  </si>
+  <si>
+    <t>Kein Bedarf an medizinischer Versorgung</t>
+  </si>
+  <si>
+    <t>health-very-good</t>
   </si>
   <si>
     <t>Sehr gut</t>
   </si>
   <si>
-    <t>hs-good</t>
+    <t>health-good</t>
   </si>
   <si>
     <t>Gut</t>
   </si>
   <si>
-    <t>hs-fair</t>
+    <t>health-fair</t>
   </si>
   <si>
     <t>Mittelmäßig</t>
   </si>
   <si>
-    <t>hs-poor</t>
+    <t>health-poor</t>
   </si>
   <si>
     <t>Schlecht</t>
   </si>
   <si>
-    <t>hs-very-poor</t>
+    <t>health-very-poor</t>
   </si>
   <si>
     <t>Sehr schlecht</t>
@@ -408,193 +450,193 @@
     <t>Zu keinem Zeitpunkt</t>
   </si>
   <si>
-    <t>dh-daily-or-more</t>
+    <t>diet-daily-or-more</t>
   </si>
   <si>
     <t>Täglich oder mehrmals täglich</t>
   </si>
   <si>
-    <t>dh-4-6-per-week</t>
+    <t>diet-4-6-per-week</t>
   </si>
   <si>
     <t>4 bis 6 Mal pro Woche</t>
   </si>
   <si>
-    <t>dh-1-3-per-week</t>
+    <t>diet-1-3-per-week</t>
   </si>
   <si>
     <t>1 bis 3 Mal pro Woche</t>
   </si>
   <si>
-    <t>dh-less-than-once-per-week</t>
+    <t>diet-less-than-once-per-week</t>
   </si>
   <si>
     <t>Weniger als einmal pro Woche</t>
   </si>
   <si>
-    <t>dh-never</t>
-  </si>
-  <si>
-    <t>dh-daily-or-nearly-daily</t>
+    <t>diet-never</t>
+  </si>
+  <si>
+    <t>diet-daily-or-nearly-daily</t>
   </si>
   <si>
     <t>Täglich oder beinahe täglich</t>
   </si>
   <si>
-    <t>dh-less-often-than-once-per-week</t>
+    <t>diet-less-often-than-once-per-week</t>
   </si>
   <si>
     <t>Seltener als einmal pro Woche</t>
   </si>
   <si>
-    <t>dh-3-4-per-week</t>
+    <t>diet-3-4-per-week</t>
   </si>
   <si>
     <t>3 bis 4 Mal pro Woche</t>
   </si>
   <si>
-    <t>dh-1-2-per-week</t>
+    <t>diet-1-2-per-week</t>
   </si>
   <si>
     <t>1 bis 2 Mal pro Woche</t>
   </si>
   <si>
-    <t>dh-1-2-per-month</t>
+    <t>diet-1-2-per-month</t>
   </si>
   <si>
     <t>1 bis 2 Mal pro Monat</t>
   </si>
   <si>
-    <t>dh-less-than-once-per-month</t>
+    <t>diet-less-than-once-per-month</t>
   </si>
   <si>
     <t>Seltener als einmal pro Monat</t>
   </si>
   <si>
-    <t>pe-never-or-rarely</t>
+    <t>activity-never-or-rarely</t>
   </si>
   <si>
     <t>Nie oder seltener als einmal pro Woche</t>
   </si>
   <si>
-    <t>pe-1-day</t>
+    <t>activity-1-day</t>
   </si>
   <si>
     <t>1 Tag pro Woche</t>
   </si>
   <si>
-    <t>pe-2-days</t>
+    <t>activity-2-days</t>
   </si>
   <si>
     <t>2 Tage pro Woche</t>
   </si>
   <si>
-    <t>pe-3-days</t>
+    <t>activity-3-days</t>
   </si>
   <si>
     <t>3 Tage pro Woche</t>
   </si>
   <si>
-    <t>pe-4-days</t>
+    <t>activity-4-days</t>
   </si>
   <si>
     <t>4 Tage pro Woche</t>
   </si>
   <si>
-    <t>pe-5-days</t>
+    <t>activity-5-days</t>
   </si>
   <si>
     <t>5 Tage pro Woche</t>
   </si>
   <si>
-    <t>pe-6-days</t>
+    <t>activity-6-days</t>
   </si>
   <si>
     <t>6 Tage pro Woche</t>
   </si>
   <si>
-    <t>pe-7-days</t>
+    <t>activity-7-days</t>
   </si>
   <si>
     <t>7 Tage pro Woche</t>
   </si>
   <si>
-    <t>pe-10-29-min</t>
+    <t>activity-10-29-min</t>
   </si>
   <si>
     <t>10 bis 29 Minuten pro Tag</t>
   </si>
   <si>
-    <t>pe-30-59-min</t>
+    <t>activity-30-59-min</t>
   </si>
   <si>
     <t>30 bis 59 Minuten pro Tag</t>
   </si>
   <si>
-    <t>pe-1h-under-2h</t>
+    <t>activity-1h-under-2h</t>
   </si>
   <si>
     <t>1 Stunde bis unter 2 Stunden pro Tag</t>
   </si>
   <si>
-    <t>pe-2h-under-3h</t>
+    <t>activity-2h-under-3h</t>
   </si>
   <si>
     <t>2 Stunden bis unter 3 Stunden pro Tag</t>
   </si>
   <si>
-    <t>pe-3h-or-more</t>
+    <t>activity-3h-or-more</t>
   </si>
   <si>
     <t>3 Stunden pro Tag oder mehr</t>
   </si>
   <si>
-    <t>pe-sitting-or-standing</t>
+    <t>activity-sitting-or-standing</t>
   </si>
   <si>
     <t>Vorwiegend sitzen oder stehen</t>
   </si>
   <si>
-    <t>pe-walking-or-moderate</t>
+    <t>activity-walking-or-moderate</t>
   </si>
   <si>
     <t>Vorwiegend gehen oder mäßig anstrengende körperliche Tätigkeiten</t>
   </si>
   <si>
-    <t>pe-heavy-physical-work</t>
+    <t>activity-heavy-physical-work</t>
   </si>
   <si>
     <t>Vorwiegend schwere körperliche Arbeit oder körperlich beanspruchende Tätigkeiten</t>
   </si>
   <si>
-    <t>pe-no-work-activities</t>
+    <t>activity-no-work-activities</t>
   </si>
   <si>
     <t>Ich führe keine arbeitsbezogenen Tätigkeiten aus</t>
   </si>
   <si>
-    <t>sk5-daily-1h-or-more</t>
+    <t>smoke-daily-1h-or-more</t>
   </si>
   <si>
     <t>Täglich, eine Stunde oder mehr pro Tag</t>
   </si>
   <si>
-    <t>sk5-daily-less-than-1h</t>
+    <t>smoke-daily-less-than-1h</t>
   </si>
   <si>
     <t>Täglich, weniger als 1 Stunde pro Tag</t>
   </si>
   <si>
-    <t>sk5-at-least-weekly</t>
+    <t>smoke-at-least-weekly</t>
   </si>
   <si>
     <t>Mindestens einmal pro Woche (aber nicht täglich)</t>
   </si>
   <si>
-    <t>sk5-less-than-weekly</t>
-  </si>
-  <si>
-    <t>sk5-never-or-rarely</t>
+    <t>smoke-less-than-weekly</t>
+  </si>
+  <si>
+    <t>smoke-never-or-rarely</t>
   </si>
   <si>
     <t>Nie oder fast nie</t>
@@ -675,28 +717,28 @@
     <t>Immer</t>
   </si>
   <si>
-    <t>kig-never</t>
-  </si>
-  <si>
-    <t>kig-seldom</t>
+    <t>child-never</t>
+  </si>
+  <si>
+    <t>child-seldom</t>
   </si>
   <si>
     <t>Selten</t>
   </si>
   <si>
-    <t>kig-sometimes</t>
+    <t>child-sometimes</t>
   </si>
   <si>
     <t>Manchmal</t>
   </si>
   <si>
-    <t>kig-often</t>
+    <t>child-often</t>
   </si>
   <si>
     <t>Oft</t>
   </si>
   <si>
-    <t>kig-always</t>
+    <t>child-always</t>
   </si>
   <si>
     <t>socio-employed</t>
@@ -747,6 +789,66 @@
     <t>Sonstiges</t>
   </si>
   <si>
+    <t>socio-apprentice</t>
+  </si>
+  <si>
+    <t>Lehrling</t>
+  </si>
+  <si>
+    <t>socio-worker</t>
+  </si>
+  <si>
+    <t>Arbeiter:in</t>
+  </si>
+  <si>
+    <t>socio-employee</t>
+  </si>
+  <si>
+    <t>Angestellte:r</t>
+  </si>
+  <si>
+    <t>socio-civil-servant-contract</t>
+  </si>
+  <si>
+    <t>Vertragsbedienstete:r</t>
+  </si>
+  <si>
+    <t>socio-civil-servant</t>
+  </si>
+  <si>
+    <t>Beamt:in</t>
+  </si>
+  <si>
+    <t>socio-freelancer</t>
+  </si>
+  <si>
+    <t>Freie:r Dienstnehmer:in</t>
+  </si>
+  <si>
+    <t>socio-self-employed</t>
+  </si>
+  <si>
+    <t>Selbstständige:r</t>
+  </si>
+  <si>
+    <t>socio-unpaid-family-helper</t>
+  </si>
+  <si>
+    <t>Unbezahlt Mithelfende:r im Familienbetrieb</t>
+  </si>
+  <si>
+    <t>socio-part-time</t>
+  </si>
+  <si>
+    <t>Teilzeit</t>
+  </si>
+  <si>
+    <t>socio-full-time</t>
+  </si>
+  <si>
+    <t>Vollzeit</t>
+  </si>
+  <si>
     <t>socio-compulsory-school</t>
   </si>
   <si>
@@ -781,6 +883,780 @@
   </si>
   <si>
     <t>Anderer Abschluss nach der Matura</t>
+  </si>
+  <si>
+    <t>socio-completed</t>
+  </si>
+  <si>
+    <t>Abgeschlossen</t>
+  </si>
+  <si>
+    <t>socio-not-completed</t>
+  </si>
+  <si>
+    <t>Nicht abgeschlossen</t>
+  </si>
+  <si>
+    <t>socio-voc-under-2y</t>
+  </si>
+  <si>
+    <t>Kürzer als 2 Jahre</t>
+  </si>
+  <si>
+    <t>socio-voc-2y-or-more</t>
+  </si>
+  <si>
+    <t>2 Jahre und länger</t>
+  </si>
+  <si>
+    <t>socio-voc-health-diploma</t>
+  </si>
+  <si>
+    <t>Diplomabschluss in der Gesundheits- und Krankenpflege</t>
+  </si>
+  <si>
+    <t>socio-matura-ahs</t>
+  </si>
+  <si>
+    <t>AHS wie zum Beispiel Gymnasium, Realgymnasium, ORG</t>
+  </si>
+  <si>
+    <t>socio-matura-bhs</t>
+  </si>
+  <si>
+    <t>BHS wie zum Beispiel HAK, HTL, HBLA</t>
+  </si>
+  <si>
+    <t>socio-matura-apprenticeship</t>
+  </si>
+  <si>
+    <t>Lehre mit Matura oder Berufsreifeprüfung</t>
+  </si>
+  <si>
+    <t>socio-degree-bachelor</t>
+  </si>
+  <si>
+    <t>Bachelor/Bakkalaureat</t>
+  </si>
+  <si>
+    <t>socio-degree-master</t>
+  </si>
+  <si>
+    <t>Master-, Magister-, Diplomabschluss</t>
+  </si>
+  <si>
+    <t>socio-degree-doctorate-first</t>
+  </si>
+  <si>
+    <t>Doktorat als Erstabschluss</t>
+  </si>
+  <si>
+    <t>socio-degree-postgraduate</t>
+  </si>
+  <si>
+    <t>Postgradualer Lehrgang wie zum Beispiel MBA, MAS, MSc</t>
+  </si>
+  <si>
+    <t>socio-degree-doctorate-after</t>
+  </si>
+  <si>
+    <t>Doktorat nach akademischem Abschluss</t>
+  </si>
+  <si>
+    <t>socio-other-academy</t>
+  </si>
+  <si>
+    <t>Akademie, wie zum Beispiel Pädak, SozAK, Med. Tech. Akad, MilAK</t>
+  </si>
+  <si>
+    <t>socio-other-kolleg</t>
+  </si>
+  <si>
+    <t>Kolleg, Abiturient:innenlehrgang an einer BHS</t>
+  </si>
+  <si>
+    <t>socio-other-uni-lehrgang</t>
+  </si>
+  <si>
+    <t>Hochschul-/Universitätslehrgang als akademisch geprüfte:r 'Berufsbezeichnung'</t>
+  </si>
+  <si>
+    <t>socio-add-master-craftsperson</t>
+  </si>
+  <si>
+    <t>Meister:innen- oder Werkmeister:innenprüfung</t>
+  </si>
+  <si>
+    <t>socio-add-health-diploma</t>
+  </si>
+  <si>
+    <t>Diplomabschluss der Gesundheits- und Krankenpflege</t>
+  </si>
+  <si>
+    <t>socio-add-other</t>
+  </si>
+  <si>
+    <t>Anderes</t>
+  </si>
+  <si>
+    <t>socio-add-none</t>
+  </si>
+  <si>
+    <t>Keine weitere Ausbildung</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-600</t>
+  </si>
+  <si>
+    <t>Bis 600 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-900</t>
+  </si>
+  <si>
+    <t>Bis 900 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-1200</t>
+  </si>
+  <si>
+    <t>Bis 1 200 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-1500</t>
+  </si>
+  <si>
+    <t>Bis 1 500 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-1800</t>
+  </si>
+  <si>
+    <t>Bis 1 800 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-2200</t>
+  </si>
+  <si>
+    <t>Bis 2 200 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-2600</t>
+  </si>
+  <si>
+    <t>Bis 2 600 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-3000</t>
+  </si>
+  <si>
+    <t>Bis 3 000 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-3500</t>
+  </si>
+  <si>
+    <t>Bis 3 500 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-4000</t>
+  </si>
+  <si>
+    <t>Bis 4 000 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-4500</t>
+  </si>
+  <si>
+    <t>Bis 4 500 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-5000</t>
+  </si>
+  <si>
+    <t>Bis 5 000 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-6000</t>
+  </si>
+  <si>
+    <t>Bis 6 000 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-up-to-8000</t>
+  </si>
+  <si>
+    <t>Bis 8 000 Euro</t>
+  </si>
+  <si>
+    <t>socio-income-over-8000</t>
+  </si>
+  <si>
+    <t>Mehr als 8 000 Euro</t>
+  </si>
+  <si>
+    <t>sex-male</t>
+  </si>
+  <si>
+    <t>Männlich</t>
+  </si>
+  <si>
+    <t>sex-female</t>
+  </si>
+  <si>
+    <t>Weiblich</t>
+  </si>
+  <si>
+    <t>sex-other</t>
+  </si>
+  <si>
+    <t>marital-single</t>
+  </si>
+  <si>
+    <t>Ledig</t>
+  </si>
+  <si>
+    <t>marital-married</t>
+  </si>
+  <si>
+    <t>Verheiratet oder eingetragene Partnerschaft</t>
+  </si>
+  <si>
+    <t>marital-widowed</t>
+  </si>
+  <si>
+    <t>Verwitwet oder hinterbliebene eingetragene Partnerschaft</t>
+  </si>
+  <si>
+    <t>marital-divorced</t>
+  </si>
+  <si>
+    <t>Geschieden oder aufgelöste eingetragene Partnerschaft</t>
+  </si>
+  <si>
+    <t>relation-partner</t>
+  </si>
+  <si>
+    <t>Partner:in</t>
+  </si>
+  <si>
+    <t>relation-child</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>relation-parent</t>
+  </si>
+  <si>
+    <t>Elternteil</t>
+  </si>
+  <si>
+    <t>relation-sibling</t>
+  </si>
+  <si>
+    <t>Geschwister</t>
+  </si>
+  <si>
+    <t>relation-other-member</t>
+  </si>
+  <si>
+    <t>Anderes Haushaltsmitglied</t>
+  </si>
+  <si>
+    <t>recency-within-1m</t>
+  </si>
+  <si>
+    <t>Während des letzten Monats</t>
+  </si>
+  <si>
+    <t>recency-1-3m</t>
+  </si>
+  <si>
+    <t>Vor einem bis zu 3 Monaten</t>
+  </si>
+  <si>
+    <t>recency-3-12m</t>
+  </si>
+  <si>
+    <t>Vor 3 bis zu 12 Monaten</t>
+  </si>
+  <si>
+    <t>recency-within-6m</t>
+  </si>
+  <si>
+    <t>Vor weniger als 6 Monaten</t>
+  </si>
+  <si>
+    <t>recency-6-12m</t>
+  </si>
+  <si>
+    <t>Vor 6 bis weniger als 12 Monaten</t>
+  </si>
+  <si>
+    <t>recency-within-12m</t>
+  </si>
+  <si>
+    <t>Vor weniger als 12 Monaten / Innerhalb der letzten 12 Monate</t>
+  </si>
+  <si>
+    <t>recency-12m-or-more</t>
+  </si>
+  <si>
+    <t>Vor 12 Monaten oder länger</t>
+  </si>
+  <si>
+    <t>recency-over-1y</t>
+  </si>
+  <si>
+    <t>Vor mehr als einem Jahr</t>
+  </si>
+  <si>
+    <t>recency-1-2y</t>
+  </si>
+  <si>
+    <t>Vor 1 bis weniger als 2 Jahren</t>
+  </si>
+  <si>
+    <t>recency-1-3y</t>
+  </si>
+  <si>
+    <t>Vor 1 bis weniger als 3 Jahren</t>
+  </si>
+  <si>
+    <t>recency-1-5y</t>
+  </si>
+  <si>
+    <t>Vor 1 bis weniger als 5 Jahren</t>
+  </si>
+  <si>
+    <t>recency-2-3y</t>
+  </si>
+  <si>
+    <t>Vor 2 bis weniger als 3 Jahren</t>
+  </si>
+  <si>
+    <t>recency-3-5y</t>
+  </si>
+  <si>
+    <t>Vor 3 bis weniger als 5 Jahren</t>
+  </si>
+  <si>
+    <t>recency-3y-or-more</t>
+  </si>
+  <si>
+    <t>Vor 3 Jahren oder länger</t>
+  </si>
+  <si>
+    <t>recency-5-10y</t>
+  </si>
+  <si>
+    <t>Vor 5 bis weniger als 10 Jahren</t>
+  </si>
+  <si>
+    <t>recency-5y-or-more</t>
+  </si>
+  <si>
+    <t>Vor 5 Jahren oder länger</t>
+  </si>
+  <si>
+    <t>recency-10y-or-more</t>
+  </si>
+  <si>
+    <t>Vor 10 Jahren oder länger</t>
+  </si>
+  <si>
+    <t>recency-never</t>
+  </si>
+  <si>
+    <t>Nie / Noch nie</t>
+  </si>
+  <si>
+    <t>wait-days-up-to-1</t>
+  </si>
+  <si>
+    <t>Bis zu 1 Tag</t>
+  </si>
+  <si>
+    <t>wait-days-2-7</t>
+  </si>
+  <si>
+    <t>2 bis 7 Tage</t>
+  </si>
+  <si>
+    <t>wait-days-8-14</t>
+  </si>
+  <si>
+    <t>8 bis 14 Tage</t>
+  </si>
+  <si>
+    <t>wait-days-3-4-weeks</t>
+  </si>
+  <si>
+    <t>3 bis 4 Wochen</t>
+  </si>
+  <si>
+    <t>wait-days-5-8-weeks</t>
+  </si>
+  <si>
+    <t>5 bis 8 Wochen</t>
+  </si>
+  <si>
+    <t>wait-days-over-8-weeks</t>
+  </si>
+  <si>
+    <t>Mehr als 8 Wochen</t>
+  </si>
+  <si>
+    <t>wait-op-up-to-2-weeks</t>
+  </si>
+  <si>
+    <t>Bis zu 2 Wochen</t>
+  </si>
+  <si>
+    <t>wait-op-2w-under-1m</t>
+  </si>
+  <si>
+    <t>2 Wochen bis unter 1 Monat</t>
+  </si>
+  <si>
+    <t>wait-op-1m-under-2m</t>
+  </si>
+  <si>
+    <t>1 Monat bis unter 2 Monate</t>
+  </si>
+  <si>
+    <t>wait-op-2m-under-3m</t>
+  </si>
+  <si>
+    <t>2 Monate bis unter 3 Monate</t>
+  </si>
+  <si>
+    <t>wait-op-3m-under-6m</t>
+  </si>
+  <si>
+    <t>3 Monate bis unter 6 Monate</t>
+  </si>
+  <si>
+    <t>wait-op-6m-or-more</t>
+  </si>
+  <si>
+    <t>6 Monate oder mehr</t>
+  </si>
+  <si>
+    <t>care-hours-under-5</t>
+  </si>
+  <si>
+    <t>Weniger als 5 Stunden pro Woche</t>
+  </si>
+  <si>
+    <t>care-hours-5-10</t>
+  </si>
+  <si>
+    <t>5 Stunden bis weniger als 10 Stunden pro Woche</t>
+  </si>
+  <si>
+    <t>care-hours-10-20</t>
+  </si>
+  <si>
+    <t>10 Stunden bis weniger als 20 Stunden pro Woche</t>
+  </si>
+  <si>
+    <t>care-hours-20-30</t>
+  </si>
+  <si>
+    <t>20 Stunden bis weniger als 30 Stunden pro Woche</t>
+  </si>
+  <si>
+    <t>care-hours-30-40</t>
+  </si>
+  <si>
+    <t>30 Stunden bis weniger als 40 Stunden pro Woche</t>
+  </si>
+  <si>
+    <t>care-hours-40-or-more</t>
+  </si>
+  <si>
+    <t>40 Stunden pro Woche oder mehr</t>
+  </si>
+  <si>
+    <t>care-provider-family</t>
+  </si>
+  <si>
+    <t>Ja, hauptsächlich durch ein Familienmitglied</t>
+  </si>
+  <si>
+    <t>care-provider-non-family</t>
+  </si>
+  <si>
+    <t>Ja, hauptsächlich durch ein Nicht-Familienmitglied</t>
+  </si>
+  <si>
+    <t>care-provider-none</t>
+  </si>
+  <si>
+    <t>satisfaction-quality-excellent</t>
+  </si>
+  <si>
+    <t>Hervorragend</t>
+  </si>
+  <si>
+    <t>satisfaction-quality-very-good</t>
+  </si>
+  <si>
+    <t>satisfaction-quality-good</t>
+  </si>
+  <si>
+    <t>satisfaction-quality-adequate</t>
+  </si>
+  <si>
+    <t>Ausreichend</t>
+  </si>
+  <si>
+    <t>satisfaction-quality-poor</t>
+  </si>
+  <si>
+    <t>satisfaction-service-very-satisfied</t>
+  </si>
+  <si>
+    <t>Sehr zufrieden</t>
+  </si>
+  <si>
+    <t>satisfaction-service-rather-satisfied</t>
+  </si>
+  <si>
+    <t>Eher zufrieden</t>
+  </si>
+  <si>
+    <t>satisfaction-service-moderate</t>
+  </si>
+  <si>
+    <t>satisfaction-service-rather-unsatisfied</t>
+  </si>
+  <si>
+    <t>Eher unzufrieden</t>
+  </si>
+  <si>
+    <t>satisfaction-service-very-unsatisfied</t>
+  </si>
+  <si>
+    <t>Sehr unzufrieden</t>
+  </si>
+  <si>
+    <t>satisfaction-service-not-applicable</t>
+  </si>
+  <si>
+    <t>social-support-none</t>
+  </si>
+  <si>
+    <t>Keine</t>
+  </si>
+  <si>
+    <t>social-support-1-2</t>
+  </si>
+  <si>
+    <t>1 oder 2 Personen</t>
+  </si>
+  <si>
+    <t>social-support-3-5</t>
+  </si>
+  <si>
+    <t>3 bis 5 Personen</t>
+  </si>
+  <si>
+    <t>social-support-6-or-more</t>
+  </si>
+  <si>
+    <t>6 Personen oder mehr</t>
+  </si>
+  <si>
+    <t>social-interest-a-lot</t>
+  </si>
+  <si>
+    <t>Viel</t>
+  </si>
+  <si>
+    <t>social-interest-some</t>
+  </si>
+  <si>
+    <t>social-interest-neither</t>
+  </si>
+  <si>
+    <t>Weder viel noch wenig</t>
+  </si>
+  <si>
+    <t>social-interest-little</t>
+  </si>
+  <si>
+    <t>Wenig</t>
+  </si>
+  <si>
+    <t>social-interest-none</t>
+  </si>
+  <si>
+    <t>Keinerlei Anteilnahme und Interesse</t>
+  </si>
+  <si>
+    <t>social-help-very-easy</t>
+  </si>
+  <si>
+    <t>Sehr einfach</t>
+  </si>
+  <si>
+    <t>social-help-easy</t>
+  </si>
+  <si>
+    <t>Einfach</t>
+  </si>
+  <si>
+    <t>social-help-possible</t>
+  </si>
+  <si>
+    <t>Möglich</t>
+  </si>
+  <si>
+    <t>social-help-difficult</t>
+  </si>
+  <si>
+    <t>Schwierig</t>
+  </si>
+  <si>
+    <t>social-help-very-difficult</t>
+  </si>
+  <si>
+    <t>Sehr schwierig</t>
+  </si>
+  <si>
+    <t>alcohol-wkday-all-4</t>
+  </si>
+  <si>
+    <t>An allen 4 Tagen</t>
+  </si>
+  <si>
+    <t>alcohol-wkday-3</t>
+  </si>
+  <si>
+    <t>An 3 Tagen</t>
+  </si>
+  <si>
+    <t>alcohol-wkday-2</t>
+  </si>
+  <si>
+    <t>An 2 Tagen</t>
+  </si>
+  <si>
+    <t>alcohol-wkday-1</t>
+  </si>
+  <si>
+    <t>An 1 Tag</t>
+  </si>
+  <si>
+    <t>alcohol-wkday-none</t>
+  </si>
+  <si>
+    <t>An keinem dieser 4 Tage</t>
+  </si>
+  <si>
+    <t>alcohol-wkend-all-3</t>
+  </si>
+  <si>
+    <t>An allen 3 Tagen</t>
+  </si>
+  <si>
+    <t>alcohol-wkend-2</t>
+  </si>
+  <si>
+    <t>alcohol-wkend-1</t>
+  </si>
+  <si>
+    <t>alcohol-wkend-none</t>
+  </si>
+  <si>
+    <t>An keinem dieser 3 Tage</t>
+  </si>
+  <si>
+    <t>practice-health-fund</t>
+  </si>
+  <si>
+    <t>Kassenordination</t>
+  </si>
+  <si>
+    <t>practice-private</t>
+  </si>
+  <si>
+    <t>Wahlordination/Privatordination</t>
+  </si>
+  <si>
+    <t>insurance-fully-covered</t>
+  </si>
+  <si>
+    <t>Ja, die gesamten Kosten wurden übernommen</t>
+  </si>
+  <si>
+    <t>insurance-partially-covered</t>
+  </si>
+  <si>
+    <t>Ja, ein Teil der Kosten wurde übernommen</t>
+  </si>
+  <si>
+    <t>insurance-not-covered</t>
+  </si>
+  <si>
+    <t>Nein, die Kosten wurden nicht übernommen</t>
+  </si>
+  <si>
+    <t>barrier-too-expensive</t>
+  </si>
+  <si>
+    <t>Konnte es mir nicht leisten (zu teuer oder nicht von der Krankenkasse übernommen)</t>
+  </si>
+  <si>
+    <t>barrier-waiting-list</t>
+  </si>
+  <si>
+    <t>Warteliste</t>
+  </si>
+  <si>
+    <t>barrier-no-time</t>
+  </si>
+  <si>
+    <t>Keine Zeit wegen Arbeit/Betreuung von Kindern oder anderen Personen</t>
+  </si>
+  <si>
+    <t>barrier-too-far</t>
+  </si>
+  <si>
+    <t>Zu weite Anreise/kein Verkehrsmittel verfügbar</t>
+  </si>
+  <si>
+    <t>barrier-confidentiality-concerns</t>
+  </si>
+  <si>
+    <t>Bedenken hinsichtlich Vertraulichkeit und Diskretion</t>
+  </si>
+  <si>
+    <t>barrier-fear-of-reactions</t>
+  </si>
+  <si>
+    <t>Angst vor negativen Reaktionen oder Kommentaren von Familie, Freund:innen oder Kolleg:innen</t>
+  </si>
+  <si>
+    <t>barrier-fear-of-treatment</t>
+  </si>
+  <si>
+    <t>Angst vor der Beratung oder Behandlung (zum Beispiel Angst vor einem negativen Ausgang oder Angst vor den Nebenwirkungen von Medikamenten)</t>
+  </si>
+  <si>
+    <t>barrier-no-knowledge</t>
+  </si>
+  <si>
+    <t>Kein Wissen darüber, wo man Hilfe suchen kann</t>
+  </si>
+  <si>
+    <t>barrier-other-reason</t>
+  </si>
+  <si>
+    <t>Anderer Grund</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D263"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1497,7 +2373,7 @@
         <v>106</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D33" s="2"/>
     </row>
@@ -1506,10 +2382,10 @@
         <v>43</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D34" s="2"/>
     </row>
@@ -1518,10 +2394,10 @@
         <v>43</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D35" s="2"/>
     </row>
@@ -1530,10 +2406,10 @@
         <v>43</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D36" s="2"/>
     </row>
@@ -1542,10 +2418,10 @@
         <v>43</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D37" s="2"/>
     </row>
@@ -1554,10 +2430,10 @@
         <v>43</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D38" s="2"/>
     </row>
@@ -1566,10 +2442,10 @@
         <v>43</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D39" s="2"/>
     </row>
@@ -1578,10 +2454,10 @@
         <v>43</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D40" s="2"/>
     </row>
@@ -1701,7 +2577,7 @@
         <v>139</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="D50" s="2"/>
     </row>
@@ -1710,10 +2586,10 @@
         <v>43</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D51" s="2"/>
     </row>
@@ -1722,10 +2598,10 @@
         <v>43</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D52" s="2"/>
     </row>
@@ -1734,10 +2610,10 @@
         <v>43</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D53" s="2"/>
     </row>
@@ -1746,10 +2622,10 @@
         <v>43</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D54" s="2"/>
     </row>
@@ -1758,10 +2634,10 @@
         <v>43</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D55" s="2"/>
     </row>
@@ -1770,10 +2646,10 @@
         <v>43</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D56" s="2"/>
     </row>
@@ -1782,10 +2658,10 @@
         <v>43</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="D57" s="2"/>
     </row>
@@ -2025,7 +2901,7 @@
         <v>192</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="D77" s="2"/>
     </row>
@@ -2034,10 +2910,10 @@
         <v>43</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D78" s="2"/>
     </row>
@@ -2046,10 +2922,10 @@
         <v>43</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>103</v>
+        <v>197</v>
       </c>
       <c r="D79" s="2"/>
     </row>
@@ -2058,10 +2934,10 @@
         <v>43</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D80" s="2"/>
     </row>
@@ -2070,10 +2946,10 @@
         <v>43</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>67</v>
+        <v>201</v>
       </c>
       <c r="D81" s="2"/>
     </row>
@@ -2082,10 +2958,10 @@
         <v>43</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>108</v>
+        <v>203</v>
       </c>
       <c r="D82" s="2"/>
     </row>
@@ -2094,10 +2970,10 @@
         <v>43</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>110</v>
+        <v>205</v>
       </c>
       <c r="D83" s="2"/>
     </row>
@@ -2106,10 +2982,10 @@
         <v>43</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="D84" s="2"/>
     </row>
@@ -2118,10 +2994,10 @@
         <v>43</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D85" s="2"/>
     </row>
@@ -2130,10 +3006,10 @@
         <v>43</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="D86" s="2"/>
     </row>
@@ -2142,10 +3018,10 @@
         <v>43</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D87" s="2"/>
     </row>
@@ -2154,10 +3030,10 @@
         <v>43</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="D88" s="2"/>
     </row>
@@ -2166,10 +3042,10 @@
         <v>43</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>211</v>
+        <v>122</v>
       </c>
       <c r="D89" s="2"/>
     </row>
@@ -2178,10 +3054,10 @@
         <v>43</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>213</v>
+        <v>124</v>
       </c>
       <c r="D90" s="2"/>
     </row>
@@ -2190,10 +3066,10 @@
         <v>43</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>215</v>
+        <v>117</v>
       </c>
       <c r="D91" s="2"/>
     </row>
@@ -2229,7 +3105,7 @@
         <v>220</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>112</v>
+        <v>221</v>
       </c>
       <c r="D94" s="2"/>
     </row>
@@ -2238,10 +3114,10 @@
         <v>43</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D95" s="2"/>
     </row>
@@ -2250,10 +3126,10 @@
         <v>43</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D96" s="2"/>
     </row>
@@ -2262,10 +3138,10 @@
         <v>43</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D97" s="2"/>
     </row>
@@ -2274,10 +3150,10 @@
         <v>43</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="D98" s="2"/>
     </row>
@@ -2286,10 +3162,10 @@
         <v>43</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D99" s="2"/>
     </row>
@@ -2298,10 +3174,10 @@
         <v>43</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D100" s="2"/>
     </row>
@@ -2310,10 +3186,10 @@
         <v>43</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>233</v>
+        <v>126</v>
       </c>
       <c r="D101" s="2"/>
     </row>
@@ -2322,10 +3198,10 @@
         <v>43</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D102" s="2"/>
     </row>
@@ -2334,10 +3210,10 @@
         <v>43</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D103" s="2"/>
     </row>
@@ -2346,10 +3222,10 @@
         <v>43</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D104" s="2"/>
     </row>
@@ -2358,10 +3234,10 @@
         <v>43</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D105" s="2"/>
     </row>
@@ -2448,6 +3324,1818 @@
         <v>255</v>
       </c>
       <c r="D112" s="2"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="D113" s="2"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="D114" s="2"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="D115" s="2"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="D116" s="2"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="D117" s="2"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="D118" s="2"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="D119" s="2"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="D120" s="2"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="D121" s="2"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="D122" s="2"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="D123" s="2"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="D124" s="2"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="D125" s="2"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="D126" s="2"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="D127" s="2"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="D128" s="2"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="D129" s="2"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="D130" s="2"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="D131" s="2"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="D132" s="2"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="D133" s="2"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="D134" s="2"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="D135" s="2"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="D136" s="2"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="D137" s="2"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="D138" s="2"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="D139" s="2"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="D140" s="2"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="D141" s="2"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="D142" s="2"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="D143" s="2"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="D144" s="2"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="D145" s="2"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C146" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="D146" s="2"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C147" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="D147" s="2"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C148" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="D148" s="2"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C149" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="D149" s="2"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="D150" s="2"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C151" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="D151" s="2"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="D152" s="2"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C153" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="D153" s="2"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="D154" s="2"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="C155" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="D155" s="2"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C156" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="D156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="C157" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="D157" s="2"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C158" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="D158" s="2"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C159" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="D159" s="2"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="D160" s="2"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C161" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="D161" s="2"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C162" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="D162" s="2"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C163" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="D163" s="2"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="D164" s="2"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="D165" s="2"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C166" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="D166" s="2"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C167" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="D167" s="2"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C168" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="D168" s="2"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C169" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="D169" s="2"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C170" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="D170" s="2"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C171" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="D171" s="2"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C172" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="D172" s="2"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C173" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="D173" s="2"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C174" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="D174" s="2"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C175" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="D175" s="2"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C176" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="D176" s="2"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C177" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="D177" s="2"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C178" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="D178" s="2"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="D179" s="2"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C180" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="D180" s="2"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C181" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="D181" s="2"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C182" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="D182" s="2"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C183" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="D183" s="2"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C184" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="D184" s="2"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C185" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="D185" s="2"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C186" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="D186" s="2"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C187" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="D187" s="2"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C188" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="D188" s="2"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C189" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="D189" s="2"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C190" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="D190" s="2"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="D191" s="2"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C192" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="D192" s="2"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C193" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="D193" s="2"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C194" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="D194" s="2"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="D195" s="2"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C196" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="D196" s="2"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C197" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="D197" s="2"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C198" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="D198" s="2"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="D199" s="2"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C200" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="D200" s="2"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="D201" s="2"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C202" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="D202" s="2"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="C203" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="D203" s="2"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C204" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="D204" s="2"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="D205" s="2"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C206" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="D206" s="2"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C207" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="D207" s="2"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C208" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="D208" s="2"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C209" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="D209" s="2"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C210" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="D210" s="2"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C211" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="D211" s="2"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C212" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="D212" s="2"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C213" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="D213" s="2"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C214" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="D214" s="2"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C215" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D215" s="2"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C216" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="D216" s="2"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C217" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D217" s="2"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="D218" s="2"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C219" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="D219" s="2"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C220" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="D220" s="2"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C221" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="D221" s="2"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C222" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="D222" s="2"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C223" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D223" s="2"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C224" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="D224" s="2"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C225" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="D225" s="2"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C226" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="D226" s="2"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C227" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="D227" s="2"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C228" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="D228" s="2"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C229" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="D229" s="2"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C230" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="D230" s="2"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B231" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C231" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="D231" s="2"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C232" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="D232" s="2"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C233" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="D233" s="2"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C234" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="D234" s="2"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C235" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="D235" s="2"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C236" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="D236" s="2"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C237" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="D237" s="2"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B238" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C238" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="D238" s="2"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B239" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C239" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="D239" s="2"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C240" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="D240" s="2"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B241" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C241" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="D241" s="2"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C242" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="D242" s="2"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B243" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C243" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="D243" s="2"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C244" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="D244" s="2"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C245" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="D245" s="2"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C246" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="D246" s="2"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C247" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="D247" s="2"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C248" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="D248" s="2"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C249" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="D249" s="2"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C250" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="D250" s="2"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C251" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="D251" s="2"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C252" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="D252" s="2"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C253" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="D253" s="2"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C254" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="D254" s="2"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C255" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="D255" s="2"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B256" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C256" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="D256" s="2"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B257" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C257" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="D257" s="2"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C258" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="D258" s="2"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C259" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="D259" s="2"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C260" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="D260" s="2"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C261" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="D261" s="2"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C262" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="D262" s="2"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C263" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="D263" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:52+00:00</t>
+    <t>2026-06-16T06:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Vollständige Antwortmöglichkeiten aus dem ATHIS Fragebogen (Österreichische Gesundheitsbefragung, STATISTIK AUSTRIA, Version 31.03.2025). Codes sind englisch; Display-Werte bleiben deutsch. Gruppiert nach Skalentypen. Hinweis: Bestehende PreNUDGE CodeSystems bleiben gültig – whoqol-bref-scale (LQ16-Zufriedenheitsskala), prenudge-nutrition-consumption-frequency (DH1/DH3 numerische Codes), prenudge-alcoholuse-frequency (AL1 SNOMED-basiert).</t>
+    <t>Vollständige Antwortmöglichkeiten aus dem ATHIS Fragebogen (Österreichische Gesundheitsbefragung, STATISTIK AUSTRIA, Version 31.03.2025). Codes sind englisch; Display-Werte bleiben deutsch. Gruppiert nach Skalentypen. Hinweis: Bestehende PreNUDGE CodeSystems bleiben gültig – whoqol-bref-scale (LQ16-Zufriedenheitsskala), prenudge-alcoholuse-frequency (AL1 SNOMED-basiert).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>ATHIS – Antwortmöglichkeiten</t>
+    <t>AT PreNUDGE ATHIS Answer Options</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Vollständige Antwortmöglichkeiten aus dem ATHIS Fragebogen (Österreichische Gesundheitsbefragung, STATISTIK AUSTRIA, Version 31.03.2025). Codes sind englisch; Display-Werte bleiben deutsch. Gruppiert nach Skalentypen. Hinweis: Bestehende PreNUDGE CodeSystems bleiben gültig – whoqol-bref-scale (LQ16-Zufriedenheitsskala), prenudge-alcoholuse-frequency (AL1 SNOMED-basiert).</t>
+    <t>Complete set of answer options from the ATHIS questionnaire (Austrian Health Interview Survey (Österreichische Gesundheitsbefragung, STATISTIK AUSTRIA, version 2025-03-31). Codes are in English; display values remain in German (original questionnaire wording). Grouped by scale type. Note: existing PreNUDGE CodeSystems remain valid – whoqol-bref-scale (LQ16 satisfaction scale), prenudge-alcoholuse-frequency (AL1, SNOMED-based).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
